--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-07).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-07).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-174</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>R$ 1.591.647,88</t>
-  </si>
-  <si>
-    <t>R$ 8.421,42
-R$ 8.543,05</t>
-  </si>
-  <si>
-    <t>157.6%
-160.7%</t>
-  </si>
-  <si>
-    <t>92.2</t>
-  </si>
-  <si>
-    <t>131.0%</t>
-  </si>
-  <si>
-    <t>52.7%</t>
-  </si>
-  <si>
-    <t>10.7%</t>
+175</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>R$ 1.597.733,91</t>
+  </si>
+  <si>
+    <t>R$ 8.409,13
+R$ 8.529,01</t>
+  </si>
+  <si>
+    <t>157.5%
+160.6%</t>
+  </si>
+  <si>
+    <t>92.1</t>
+  </si>
+  <si>
+    <t>130.9%</t>
+  </si>
+  <si>
+    <t>52.5%</t>
+  </si>
+  <si>
+    <t>10.5%</t>
   </si>
   <si>
     <t>2.3%</t>
@@ -947,34 +947,34 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>35.4</t>
-  </si>
-  <si>
-    <t>47.8%</t>
-  </si>
-  <si>
-    <t>27.8%</t>
+    <t>35.7</t>
+  </si>
+  <si>
+    <t>47.7%</t>
+  </si>
+  <si>
+    <t>28.0%</t>
   </si>
   <si>
     <t>8.8</t>
   </si>
   <si>
-    <t>10.8</t>
+    <t>11.0</t>
   </si>
   <si>
     <t>20.3</t>
   </si>
   <si>
-    <t>26.1</t>
-  </si>
-  <si>
-    <t>49.3%</t>
-  </si>
-  <si>
-    <t>-R$ 46.909,60</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>26.4</t>
+  </si>
+  <si>
+    <t>49.2%</t>
+  </si>
+  <si>
+    <t>-R$ 46.987,60</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -10137,7 +10137,7 @@
         <v>19647</v>
       </c>
       <c r="B69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C69" s="4">
         <v>44</v>
@@ -10171,27 +10171,61 @@
       <c t="s" r="N69" s="4">
         <v>52</v>
       </c>
-      <c r="O69" s="5"/>
-      <c r="P69" s="5"/>
-      <c r="Q69" s="6"/>
-      <c r="R69" s="7"/>
-      <c r="S69" s="6"/>
-      <c r="T69" s="6"/>
-      <c r="U69" s="6"/>
-      <c r="V69" s="6"/>
-      <c r="W69" s="6"/>
-      <c r="X69" s="8"/>
-      <c r="Y69" s="6"/>
-      <c r="Z69" s="6"/>
-      <c r="AA69" s="8"/>
-      <c r="AB69" s="8"/>
+      <c r="O69" s="5">
+        <v>6086.0299999999997</v>
+      </c>
+      <c r="P69" s="5">
+        <v>6086.0299999999997</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>1.4482199605776578</v>
+      </c>
+      <c r="R69" s="7">
+        <v>67</v>
+      </c>
+      <c r="S69" s="6">
+        <v>1.161290322580645</v>
+      </c>
+      <c r="T69" s="6">
+        <v>-0.13049327722669787</v>
+      </c>
+      <c r="U69" s="6">
+        <v>-0.4297425415254279</v>
+      </c>
+      <c r="V69" s="6">
+        <v>0.020369436233472395</v>
+      </c>
+      <c r="W69" s="6">
+        <v>-0.011539706508183496</v>
+      </c>
+      <c r="X69" s="8">
+        <v>96.96632653061225</v>
+      </c>
+      <c r="Y69" s="6">
+        <v>0.22448979591836735</v>
+      </c>
+      <c r="Z69" s="6">
+        <v>0.77551020408163263</v>
+      </c>
+      <c r="AA69" s="8">
+        <v>7.4921573529411765</v>
+      </c>
+      <c r="AB69" s="8">
+        <v>63.632312244897953</v>
+      </c>
       <c r="AC69" s="8">
         <v>71.525121999999996</v>
       </c>
-      <c r="AD69" s="8"/>
-      <c r="AE69" s="6"/>
+      <c r="AD69" s="8">
+        <v>79.394218367346937</v>
+      </c>
+      <c r="AE69" s="6">
+        <v>0.12244897959183673</v>
+      </c>
       <c r="AF69" s="9"/>
-      <c r="AG69" s="5"/>
+      <c r="AG69" s="5">
+        <v>-78</v>
+      </c>
       <c r="AH69" s="10">
         <v>2</v>
       </c>
@@ -11031,7 +11065,7 @@
         <v>0.016253450011701996</v>
       </c>
       <c r="W76" s="6">
-        <v>-0.012030760325107775</v>
+        <v>-0.013851840260130536</v>
       </c>
       <c r="X76" s="8">
         <v>31.238775510204082</v>
@@ -15437,7 +15471,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15782,7 +15816,7 @@
         <v>0</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -17312,7 +17346,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18489,7 +18523,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20807,7 +20841,7 @@
         <v>-2534.6500000000001</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -22091,7 +22125,7 @@
         <v>-1484.04</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -28254,7 +28288,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-07).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-07).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-175</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>R$ 1.597.733,91</t>
-  </si>
-  <si>
-    <t>R$ 8.409,13
-R$ 8.529,01</t>
-  </si>
-  <si>
-    <t>157.5%
-160.6%</t>
-  </si>
-  <si>
-    <t>92.1</t>
-  </si>
-  <si>
-    <t>130.9%</t>
-  </si>
-  <si>
-    <t>52.5%</t>
-  </si>
-  <si>
-    <t>10.5%</t>
+179</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>R$ 1.621.169,67</t>
+  </si>
+  <si>
+    <t>R$ 8.356,54
+R$ 8.469,34</t>
+  </si>
+  <si>
+    <t>157.3%
+160.2%</t>
+  </si>
+  <si>
+    <t>91.5</t>
+  </si>
+  <si>
+    <t>131.4%</t>
+  </si>
+  <si>
+    <t>52.0%</t>
+  </si>
+  <si>
+    <t>10.1%</t>
   </si>
   <si>
     <t>2.3%</t>
@@ -947,28 +947,28 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>35.7</t>
-  </si>
-  <si>
-    <t>47.7%</t>
-  </si>
-  <si>
-    <t>28.0%</t>
+    <t>35.8</t>
+  </si>
+  <si>
+    <t>47.8%</t>
+  </si>
+  <si>
+    <t>28.2%</t>
   </si>
   <si>
     <t>8.8</t>
   </si>
   <si>
-    <t>11.0</t>
-  </si>
-  <si>
-    <t>20.3</t>
-  </si>
-  <si>
-    <t>26.4</t>
-  </si>
-  <si>
-    <t>49.2%</t>
+    <t>11.1</t>
+  </si>
+  <si>
+    <t>20.5</t>
+  </si>
+  <si>
+    <t>26.5</t>
+  </si>
+  <si>
+    <t>49.1%</t>
   </si>
   <si>
     <t>-R$ 46.987,60</t>
@@ -4420,7 +4420,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4456,25 +4456,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>7582.7399999999998</v>
+      </c>
+      <c r="P24" s="5">
+        <v>7582.7399999999998</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>1.7047405029427503</v>
+      </c>
+      <c r="R24" s="7">
+        <v>90</v>
+      </c>
+      <c r="S24" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.32131656894473504</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.025132142207170496</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-0.0046631560623204803</v>
+      </c>
+      <c r="X24" s="8">
+        <v>27.375777333333335</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.57333333333333336</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>3.9284640449438206</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>6.7811106666666667</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>17.685333333333336</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>0</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5952,7 +5986,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5988,25 +6022,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>7354.4399999999996</v>
+      </c>
+      <c r="P36" s="5">
+        <v>7354.4399999999996</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>2.8585324393238265</v>
+      </c>
+      <c r="R36" s="7">
+        <v>84</v>
+      </c>
+      <c r="S36" s="6">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.32111924225365901</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.010679562278025247</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.068150396223233864</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.035731884412681325</v>
+      </c>
+      <c r="X36" s="8">
+        <v>63.642424675324676</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.48051948051948051</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>12.623493975903614</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>26.157777333333332</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>38.755828000000001</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>44.905411688311688</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.33766233766233766</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7869,7 +7939,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7905,25 +7975,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1000.74</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1000.74</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0.06366651077760288</v>
+      </c>
+      <c r="R51" s="7">
+        <v>11</v>
+      </c>
+      <c r="S51" s="6">
+        <v>0.22222222222222232</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.34105761736315127</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.019376161640386115</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.10853918100605552</v>
+      </c>
+      <c r="X51" s="8">
+        <v>38.075000000000003</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.0888916666666661</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>26.319042857142858</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>30.124601999999999</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>33.875</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.625</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -11065,7 +11171,7 @@
         <v>0.016253450011701996</v>
       </c>
       <c r="W76" s="6">
-        <v>-0.013851840260130536</v>
+        <v>-0.012030760325107775</v>
       </c>
       <c r="X76" s="8">
         <v>31.238775510204082</v>
@@ -12620,7 +12726,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12659,7 +12765,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12693,25 +12799,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>7497.8400000000001</v>
+      </c>
+      <c r="P89" s="5">
+        <v>7497.8400000000001</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>0.78005056799971539</v>
+      </c>
+      <c r="R89" s="7">
+        <v>72</v>
+      </c>
+      <c r="S89" s="6">
+        <v>0.75609756097560976</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.16915494329033429</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.15368603491138783</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.022538357713688208</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0067511443295669151</v>
+      </c>
+      <c r="X89" s="8">
+        <v>55.529915384615393</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.58974358974358976</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>19.541666216216218</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>15.727927027027027</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>44.944871794871794</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.15384615384615385</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16691,7 +16831,7 @@
         <v>-83.799999999999997</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -16953,7 +17093,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -18654,7 +18794,7 @@
         <v>-239.59999999999999</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20968,7 +21108,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -24203,7 +24343,9 @@
       <c r="AB179" s="8">
         <v>7.747185714285715</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>29.746130999999998</v>
+      </c>
       <c r="AD179" s="8">
         <v>36.456061038961039</v>
       </c>
